--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_284_R29.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_284_R29.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.2776</v>
+        <v>7.3661</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9461</v>
+        <v>7.2698</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3315</v>
+        <v>0.0963</v>
       </c>
       <c r="G2" t="n">
         <v>-0.0245</v>
@@ -610,13 +610,13 @@
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0855</v>
+        <v>0.174</v>
       </c>
       <c r="T2" t="n">
-        <v>1.172</v>
+        <v>0.4957</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.3218</v>
       </c>
       <c r="V2" t="n">
         <v>5.361</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.619</v>
+        <v>3.2498</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6235</v>
+        <v>2.288</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9954</v>
+        <v>0.9618</v>
       </c>
       <c r="G3" t="n">
         <v>2.036</v>
@@ -688,13 +688,13 @@
         <v>0.4639</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1191</v>
+        <v>0.7499</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4481</v>
+        <v>0.2164</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5671</v>
+        <v>0.5335</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3042</v>
+        <v>3.1532</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6761</v>
+        <v>3.2226</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3719</v>
+        <v>-0.0694</v>
       </c>
       <c r="G4" t="n">
         <v>0.8288</v>
@@ -766,13 +766,13 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.473</v>
+        <v>-0.624</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6484</v>
+        <v>-0.1019</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8246</v>
+        <v>-0.5221</v>
       </c>
       <c r="V4" t="n">
         <v>1.3247</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. BEGARIN</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3089</v>
+        <v>-0.1445</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2558</v>
+        <v>1.0055</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5647</v>
+        <v>-1.15</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1819</v>
+        <v>-0.035</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0289</v>
+        <v>0.1357</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2108</v>
+        <v>-0.1707</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5546</v>
+        <v>1.888</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5546</v>
+        <v>1.7344</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.1536</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7365</v>
+        <v>-1.923</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-1.5987</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2108</v>
+        <v>-0.3243</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.6237</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4639</v>
+        <v>2.7834</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5909</v>
+        <v>-0.7332</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2987</v>
+        <v>0.0633</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2921</v>
+        <v>-0.7964</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. THEIS</t>
+          <t>J. BEGARIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3589</v>
+        <v>-0.2753</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0871</v>
+        <v>0.2558</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2718</v>
+        <v>-0.5311</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.0996</v>
+        <v>-0.1819</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2293</v>
+        <v>0.0289</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8703</v>
+        <v>-0.2108</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2304</v>
+        <v>0.5546</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1582</v>
+        <v>0.5546</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3887</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8691</v>
+        <v>-0.7365</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3875</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4816</v>
+        <v>-0.2108</v>
       </c>
       <c r="P6" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4365</v>
+        <v>-0.5573</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4629</v>
+        <v>-0.2987</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0263</v>
+        <v>-0.2585</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>D. THEIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8391</v>
+        <v>-1.7326</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7815</v>
+        <v>-1.1919</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6205</v>
+        <v>-0.5407</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.035</v>
+        <v>-3.0996</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1357</v>
+        <v>-1.2293</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1707</v>
+        <v>-1.8703</v>
       </c>
       <c r="J7" t="n">
-        <v>1.888</v>
+        <v>-1.2304</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7344</v>
+        <v>0.1582</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1536</v>
+        <v>-1.3887</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.923</v>
+        <v>-1.8691</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5987</v>
+        <v>-1.3875</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3243</v>
+        <v>-0.4816</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.6237</v>
+        <v>-1.3917</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7834</v>
+        <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4277</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1608</v>
+        <v>0.358</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.2669</v>
+        <v>-0.2952</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6778999999999999</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1003</v>
+        <v>-2.2375</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2207</v>
+        <v>-2.4252</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1205</v>
+        <v>0.1877</v>
       </c>
       <c r="G8" t="n">
         <v>-1.7975</v>
@@ -1078,13 +1078,13 @@
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6071</v>
+        <v>0.4698</v>
       </c>
       <c r="T8" t="n">
-        <v>0.586</v>
+        <v>0.3815</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0211</v>
+        <v>0.0883</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6778999999999999</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2792</v>
+        <v>-2.8164</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3111</v>
+        <v>-1.6467</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9681</v>
+        <v>-1.1697</v>
       </c>
       <c r="G9" t="n">
         <v>-2.5899</v>
@@ -1156,13 +1156,13 @@
         <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4727</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7468</v>
+        <v>-0.0824</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2741</v>
+        <v>0.0725</v>
       </c>
       <c r="V9" t="n">
         <v>-1.6083</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5547</v>
+        <v>-3.044</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2275</v>
+        <v>-3.6496</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6727</v>
+        <v>0.6055</v>
       </c>
       <c r="G10" t="n">
         <v>-4.9922</v>
@@ -1234,13 +1234,13 @@
         <v>1.8556</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6669</v>
+        <v>1.1775</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0114</v>
+        <v>0.5665</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6783</v>
+        <v>0.6111</v>
       </c>
       <c r="V10" t="n">
         <v>1.4665</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.616300000000001</v>
+        <v>-8.255000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.0865</v>
+        <v>-4.6579</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.5299</v>
+        <v>-3.5971</v>
       </c>
       <c r="G11" t="n">
         <v>-5.69</v>
@@ -1312,13 +1312,13 @@
         <v>2.0876</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4444</v>
+        <v>-1.0831</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8057</v>
+        <v>-0.3771</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6387</v>
+        <v>-0.7059</v>
       </c>
       <c r="V11" t="n">
         <v>0.1418</v>
@@ -1345,25 +1345,25 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.856600000000002</v>
+        <v>-4.7362</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6499000000000006</v>
+        <v>0.4704000000000015</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.2068</v>
+        <v>-5.2067</v>
       </c>
       <c r="G12" t="n">
         <v>-15.5458</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.412800000000001</v>
+        <v>-2.4128</v>
       </c>
       <c r="I12" t="n">
         <v>-13.133</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.767100000000001</v>
+        <v>-1.7671</v>
       </c>
       <c r="K12" t="n">
         <v>7.368899999999999</v>
@@ -1375,7 +1375,7 @@
         <v>-13.7788</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.7818</v>
+        <v>-9.781799999999999</v>
       </c>
       <c r="O12" t="n">
         <v>-3.9971</v>
@@ -1390,16 +1390,16 @@
         <v>16.2367</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4936</v>
+        <v>-0.3735000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.101</v>
+        <v>1.2213</v>
       </c>
       <c r="U12" t="n">
         <v>-1.5945</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5439</v>
+        <v>6.543899999999999</v>
       </c>
       <c r="W12" t="n">
         <v>12.6139</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O. BRISSETT</t>
+          <t>L. WALKER IV</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.0398</v>
+        <v>3.2434</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3813</v>
+        <v>3.7521</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6585</v>
+        <v>-0.5087</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6935</v>
+        <v>3.3852</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6015</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>1.295</v>
+        <v>2.4825</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4829</v>
+        <v>3.8037</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1785</v>
+        <v>2.1545</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3044</v>
+        <v>1.6492</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2106</v>
+        <v>-0.4185</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.78</v>
+        <v>-1.2518</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9906</v>
+        <v>0.8333</v>
       </c>
       <c r="P13" t="n">
-        <v>2.0876</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1892</v>
+        <v>-0.3558</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6844</v>
+        <v>-0.1059</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5048</v>
+        <v>-0.25</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9304</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W13" t="n">
         <v>1.214</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1444</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. WALKER IV</t>
+          <t>O. BRISSETT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3112</v>
+        <v>2.7538</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0444</v>
+        <v>1.7915</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7332</v>
+        <v>0.9623</v>
       </c>
       <c r="G14" t="n">
-        <v>3.3852</v>
+        <v>0.6935</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9026999999999999</v>
+        <v>-0.6015</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4825</v>
+        <v>1.295</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8037</v>
+        <v>0.4829</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1545</v>
+        <v>0.1785</v>
       </c>
       <c r="L14" t="n">
-        <v>1.6492</v>
+        <v>0.3044</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4185</v>
+        <v>0.2106</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2518</v>
+        <v>-0.78</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8333</v>
+        <v>0.9906</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4639</v>
+        <v>2.0876</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.288</v>
+        <v>0.9032</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8136</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4744</v>
+        <v>0.8085</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6778999999999999</v>
+        <v>-0.9304</v>
       </c>
       <c r="W14" t="n">
         <v>1.214</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5361</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8069</v>
+        <v>2.0048</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9713</v>
+        <v>2.3251</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1644</v>
+        <v>-0.3203</v>
       </c>
       <c r="G15" t="n">
         <v>2.3925</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3268</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0193</v>
+        <v>0.3345</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3462</v>
+        <v>0.1902</v>
       </c>
       <c r="V15" t="n">
         <v>-1.6083</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Z. HANKINS</t>
+          <t>M. SANTOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4231</v>
+        <v>1.8229</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9434</v>
+        <v>0.4482</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5203</v>
+        <v>1.3747</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8633</v>
+        <v>2.3262</v>
       </c>
       <c r="H16" t="n">
-        <v>1.054</v>
+        <v>1.0781</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1907</v>
+        <v>1.2481</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1491</v>
+        <v>2.3941</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0755</v>
+        <v>1.1427</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0736</v>
+        <v>1.2514</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2859</v>
+        <v>-0.0679</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0216</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2643</v>
+        <v>-0.0033</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9278</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R16" t="n">
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7042</v>
+        <v>0.8885</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7943</v>
+        <v>0.3736</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0901</v>
+        <v>0.5149</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2509</v>
+        <v>1.5204</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6488</v>
+        <v>1.4129</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3979</v>
+        <v>0.1075</v>
       </c>
       <c r="G17" t="n">
         <v>1.6256</v>
@@ -1780,13 +1780,13 @@
         <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8386</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1845</v>
+        <v>-0.4204</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6541</v>
+        <v>-0.1487</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2292</v>
+        <v>1.4765</v>
       </c>
       <c r="E18" t="n">
         <v>0.8051</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4241</v>
+        <v>0.6714</v>
       </c>
       <c r="G18" t="n">
         <v>1.79</v>
@@ -1858,13 +1858,13 @@
         <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.847</v>
+        <v>-0.5996</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6976</v>
+        <v>-0.4503</v>
       </c>
       <c r="V18" t="n">
         <v>1.214</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SANTOS</t>
+          <t>Z. HANKINS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0988</v>
+        <v>1.17</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1415</v>
+        <v>1.5895</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2403</v>
+        <v>-0.4195</v>
       </c>
       <c r="G19" t="n">
-        <v>2.3262</v>
+        <v>0.8633</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0781</v>
+        <v>1.054</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2481</v>
+        <v>-0.1907</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3941</v>
+        <v>1.1491</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1427</v>
+        <v>1.0755</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2514</v>
+        <v>0.0736</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0679</v>
+        <v>-0.2859</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.0216</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0033</v>
+        <v>-0.2643</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1643</v>
+        <v>0.4512</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2161</v>
+        <v>0.4404</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3804</v>
+        <v>0.0108</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. LAVI</t>
+          <t>T. BLATT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.1493</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5664</v>
+        <v>-1.3665</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6456</v>
+        <v>1.5158</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0464</v>
+        <v>2.7511</v>
       </c>
       <c r="H20" t="n">
-        <v>0.066</v>
+        <v>1.4094</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9804</v>
+        <v>1.3417</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6284999999999999</v>
+        <v>1.697</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5917</v>
+        <v>1.6637</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0368</v>
+        <v>0.0333</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4179</v>
+        <v>1.0541</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.2543</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9436</v>
+        <v>1.3084</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8556</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>1.9606</v>
+        <v>-0.5838</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1246</v>
+        <v>-0.3497</v>
       </c>
       <c r="U20" t="n">
-        <v>0.836</v>
+        <v>-0.2341</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>-0.3943</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. BLATT</t>
+          <t>J. DIBARTOLOMEO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8159</v>
+        <v>-0.1201</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8383</v>
+        <v>-1.4087</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0225</v>
+        <v>1.2886</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7511</v>
+        <v>-0.9829</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4094</v>
+        <v>0.2318</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3417</v>
+        <v>-1.2147</v>
       </c>
       <c r="J21" t="n">
-        <v>1.697</v>
+        <v>-1.4403</v>
       </c>
       <c r="K21" t="n">
-        <v>1.6637</v>
+        <v>0.4537</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0333</v>
+        <v>-1.894</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0541</v>
+        <v>0.4574</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2543</v>
+        <v>-0.222</v>
       </c>
       <c r="O21" t="n">
-        <v>1.3084</v>
+        <v>0.6793</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.6237</v>
+        <v>1.6237</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.549</v>
+        <v>0.4531</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8215</v>
+        <v>0.0316</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7275</v>
+        <v>0.4215</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3943</v>
+        <v>-1.214</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. DIBARTOLOMEO</t>
+          <t>G. LAVI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2089</v>
+        <v>-1.0096</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8805</v>
+        <v>-1.51</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6716</v>
+        <v>0.5004</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9829</v>
+        <v>1.0464</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2318</v>
+        <v>0.066</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2147</v>
+        <v>0.9804</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.4403</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4537</v>
+        <v>0.5917</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.894</v>
+        <v>0.0368</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4574</v>
+        <v>0.4179</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.222</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6793</v>
+        <v>0.9436</v>
       </c>
       <c r="P22" t="n">
-        <v>1.6237</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6357</v>
+        <v>0.8718</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4402</v>
+        <v>0.181</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1955</v>
+        <v>0.6908</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0214</v>
+        <v>-2.1051</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5838</v>
+        <v>-1.4658</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4377</v>
+        <v>-0.6393</v>
       </c>
       <c r="G23" t="n">
         <v>2.2752</v>
@@ -2248,13 +2248,13 @@
         <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1826</v>
+        <v>1.0989</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3541</v>
+        <v>0.472</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8285</v>
+        <v>0.6269</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3361</v>
+        <v>-2.6907</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6491</v>
+        <v>-2.2388</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6871</v>
+        <v>-0.4518</v>
       </c>
       <c r="G24" t="n">
         <v>-2.6201</v>
@@ -2326,13 +2326,13 @@
         <v>0.232</v>
       </c>
       <c r="S24" t="n">
-        <v>1.1242</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>1.2819</v>
+        <v>0.6921</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1577</v>
+        <v>0.0775</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5.856800000000002</v>
+        <v>8.215599999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>4.1347</v>
+        <v>4.134600000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>1.722</v>
+        <v>4.081099999999999</v>
       </c>
       <c r="G25" t="n">
         <v>15.546</v>
       </c>
       <c r="H25" t="n">
-        <v>2.413</v>
+        <v>2.412999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>13.1329</v>
@@ -2380,10 +2380,10 @@
         <v>13.7788</v>
       </c>
       <c r="K25" t="n">
-        <v>9.781599999999999</v>
+        <v>9.781599999999997</v>
       </c>
       <c r="L25" t="n">
-        <v>3.997</v>
+        <v>3.996999999999999</v>
       </c>
       <c r="M25" t="n">
         <v>1.7671</v>
@@ -2404,13 +2404,13 @@
         <v>11.5978</v>
       </c>
       <c r="S25" t="n">
-        <v>1.4936</v>
+        <v>3.8528</v>
       </c>
       <c r="T25" t="n">
-        <v>1.5947</v>
+        <v>1.5945</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1010000000000003</v>
+        <v>2.258</v>
       </c>
       <c r="V25" t="n">
         <v>-6.543900000000001</v>
